--- a/reports/tables/SHAP_Feature_Importance_FinalModel.xlsx
+++ b/reports/tables/SHAP_Feature_Importance_FinalModel.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1645741084035099</v>
+        <v>0.1345982370804737</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04964038722696696</v>
+        <v>0.05893760188251618</v>
       </c>
     </row>
     <row r="4">
@@ -472,11 +472,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Menstrual cycle length (days)</t>
+          <t>Female age (years)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03542939775033779</v>
+        <v>0.04128509327333432</v>
       </c>
     </row>
     <row r="5">
@@ -485,11 +485,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Female age (years)</t>
+          <t>Menstrual cycle length (days)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03520155205951159</v>
+        <v>0.03340358507051803</v>
       </c>
     </row>
     <row r="6">
@@ -498,11 +498,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ratio TPMSC</t>
+          <t>Initial sperm concentration (x10⁶/mL)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02215360473284227</v>
+        <v>0.02428902123763626</v>
       </c>
     </row>
     <row r="7">
@@ -511,11 +511,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Postwash TPMSC (million)</t>
+          <t>Postwash/prewash TPMSC ratio</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02176911751512695</v>
+        <v>0.02201007782975982</v>
       </c>
     </row>
     <row r="8">
@@ -524,11 +524,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Initial sperm concentration (x10⁶/mL)</t>
+          <t>Gynecological surgical history</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01673317998542362</v>
+        <v>0.02172651967395843</v>
       </c>
     </row>
     <row r="9">
@@ -537,11 +537,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Postwash sperm count (x10⁶/mL)</t>
+          <t>Postwash TPMSC (million)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01439066743533907</v>
+        <v>0.02075220649782302</v>
       </c>
     </row>
     <row r="10">
@@ -550,11 +550,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Age FSH Interaction</t>
+          <t>Postwash sperm count (x10⁶/mL)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.01199759838556435</v>
+        <v>0.01328400050878467</v>
       </c>
     </row>
     <row r="11">
@@ -563,11 +563,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Initial TPMSC (million)</t>
+          <t>Age–FSH interaction</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0108518475025104</v>
+        <v>0.0131803641574707</v>
       </c>
     </row>
     <row r="12">
@@ -576,11 +576,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LH Baseline</t>
+          <t>Initial progressive motility (%)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.003667690258455159</v>
+        <v>0.01003463470008521</v>
       </c>
     </row>
   </sheetData>
